--- a/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_P101_pos_sample_15_tokens_0.1_temp_direct_answer_scores_09-03-1.xlsx
+++ b/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_P101_pos_sample_15_tokens_0.1_temp_direct_answer_scores_09-03-1.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5122759596469454</v>
+        <v>0.4851010316859429</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2478499688916971</v>
+        <v>0.2676575171216576</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5122759596469454</v>
+        <v>0.4850973198065574</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2478499688916971</v>
+        <v>0.2676557281303009</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4886362120775321</v>
+        <v>0.5114112452004627</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2389801701314956</v>
+        <v>0.2767598650153381</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9952076786574728</v>
+        <v>0.9954869217600784</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9827497898003604</v>
+        <v>0.9866394053678984</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2375</v>
+        <v>0.276867816091954</v>
       </c>
     </row>
   </sheetData>
